--- a/426-config---paramètre-pin-all/ig/ValueSet-tddui-discriminator-vs.xlsx
+++ b/426-config---paramètre-pin-all/ig/ValueSet-tddui-discriminator-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T15:49:47+00:00</t>
+    <t>2026-01-30T16:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
